--- a/Resultados_correcciones/Entregable/Reporte_Dip_vf_2.xlsx
+++ b/Resultados_correcciones/Entregable/Reporte_Dip_vf_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\Ivan\Laboral\EstrategiaSur\GitProjects\Proyeccion-electoral-congreso\Resultados\Entregable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be16ff5b34c21876/Documents/Trabajo/EstrategiaSur/Proyeccion-electoral-congreso/Resultados_correcciones/Entregable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C686FC-F065-42BC-AF4E-B1E40E13F657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E6C686FC-F065-42BC-AF4E-B1E40E13F657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7AC02D1-C6CE-4F97-B34B-36DDC655A858}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1665" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="16" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen de Pactos" sheetId="33" r:id="rId1"/>
@@ -56,7 +56,6 @@
     <externalReference r:id="rId39"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1334,6 +1333,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -1341,7 +1361,157 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1362,7 +1532,42 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1376,14 +1581,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1391,13 +1589,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1456,7 +1647,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1470,7 +1661,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1478,13 +1676,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1513,6 +1704,243 @@
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1582,6 +2010,149 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -1590,13 +2161,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1620,7 +2184,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1634,593 +2219,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2262,7 +2261,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2276,28 +2289,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2325,6 +2317,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
@@ -2332,14 +2331,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3212,8 +3211,8 @@
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>473075</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>173268</xdr:rowOff>
     </xdr:to>
@@ -10718,7 +10717,7 @@
       <sheetName val="resultados_proyectados_proporci"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Distrito</v>
@@ -55429,29 +55428,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7CAECAB-FB20-46F5-B407-265A1B6AF463}">
   <dimension ref="B2:AI27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" customWidth="1"/>
-    <col min="3" max="3" width="49.6328125" customWidth="1"/>
-    <col min="6" max="6" width="14.7265625" customWidth="1"/>
-    <col min="7" max="7" width="49.6328125" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" customWidth="1"/>
-    <col min="11" max="11" width="49.6328125" customWidth="1"/>
-    <col min="14" max="14" width="14.7265625" customWidth="1"/>
-    <col min="15" max="15" width="49.6328125" customWidth="1"/>
-    <col min="18" max="18" width="14.7265625" customWidth="1"/>
-    <col min="19" max="19" width="49.6328125" customWidth="1"/>
-    <col min="22" max="22" width="14.7265625" customWidth="1"/>
-    <col min="23" max="23" width="49.6328125" customWidth="1"/>
-    <col min="26" max="26" width="14.7265625" customWidth="1"/>
-    <col min="27" max="27" width="49.6328125" customWidth="1"/>
-    <col min="30" max="30" width="14.7265625" customWidth="1"/>
-    <col min="31" max="31" width="49.6328125" customWidth="1"/>
-    <col min="34" max="34" width="14.7265625" customWidth="1"/>
-    <col min="35" max="35" width="49.6328125" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" customWidth="1"/>
+    <col min="3" max="3" width="49.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" customWidth="1"/>
+    <col min="7" max="7" width="49.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" customWidth="1"/>
+    <col min="11" max="11" width="49.6640625" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" customWidth="1"/>
+    <col min="15" max="15" width="49.6640625" customWidth="1"/>
+    <col min="18" max="18" width="14.77734375" customWidth="1"/>
+    <col min="19" max="19" width="49.6640625" customWidth="1"/>
+    <col min="22" max="22" width="14.77734375" customWidth="1"/>
+    <col min="23" max="23" width="49.6640625" customWidth="1"/>
+    <col min="26" max="26" width="14.77734375" customWidth="1"/>
+    <col min="27" max="27" width="49.6640625" customWidth="1"/>
+    <col min="30" max="30" width="14.77734375" customWidth="1"/>
+    <col min="31" max="31" width="49.6640625" customWidth="1"/>
+    <col min="34" max="34" width="14.77734375" customWidth="1"/>
+    <col min="35" max="35" width="49.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
@@ -55507,7 +55506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:35" ht="77" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:35" ht="76.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
@@ -55575,7 +55574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B4" s="33" t="s">
         <v>40</v>
       </c>
@@ -55643,7 +55642,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
@@ -55699,7 +55698,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>12</v>
       </c>
@@ -55755,7 +55754,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>38</v>
       </c>
@@ -55811,7 +55810,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>17</v>
       </c>
@@ -55867,7 +55866,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>23</v>
       </c>
@@ -55923,7 +55922,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>13</v>
       </c>
@@ -55979,7 +55978,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>19</v>
       </c>
@@ -56035,7 +56034,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>15</v>
       </c>
@@ -56091,7 +56090,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>26</v>
       </c>
@@ -56147,7 +56146,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>21</v>
       </c>
@@ -56203,7 +56202,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B15" s="14" t="s">
         <v>24</v>
       </c>
@@ -56259,7 +56258,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="s">
         <v>16</v>
       </c>
@@ -56315,7 +56314,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="s">
         <v>27</v>
       </c>
@@ -56371,7 +56370,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="s">
         <v>20</v>
       </c>
@@ -56427,7 +56426,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
         <v>14</v>
       </c>
@@ -56483,7 +56482,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
         <v>22</v>
       </c>
@@ -56539,7 +56538,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B21" s="15" t="s">
         <v>45</v>
       </c>
@@ -56595,7 +56594,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
         <v>18</v>
       </c>
@@ -56651,7 +56650,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B23" s="17" t="s">
         <v>25</v>
       </c>
@@ -56707,7 +56706,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
         <v>49</v>
       </c>
@@ -56763,7 +56762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
         <v>39</v>
       </c>
@@ -56819,7 +56818,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B26" s="18" t="s">
         <v>51</v>
       </c>
@@ -56875,7 +56874,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B27" s="19" t="s">
         <v>37</v>
       </c>
@@ -56933,43 +56932,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C27">
-    <cfRule type="cellIs" dxfId="141" priority="149" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="155" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="140" priority="149" operator="equal">
       <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="150" operator="equal">
-      <formula>"p6"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="139" priority="151" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="152" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="150" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="137" priority="152" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="153" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="153" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="154" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="154" operator="equal">
       <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="155" operator="equal">
-      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:G27">
-    <cfRule type="cellIs" dxfId="134" priority="107" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="134" priority="111" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="108" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="133" priority="110" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="132" priority="109" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="110" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="131" priority="108" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="111" operator="equal">
-      <formula>"p3"</formula>
+    <cfRule type="cellIs" dxfId="130" priority="107" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="129" priority="112" operator="equal">
       <formula>"p2"</formula>
@@ -56990,31 +56989,31 @@
     <cfRule type="cellIs" dxfId="125" priority="143" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="144" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="124" priority="148" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="145" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="123" priority="147" operator="equal">
+      <formula>"p2"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="122" priority="146" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="147" operator="equal">
-      <formula>"p2"</formula>
+    <cfRule type="cellIs" dxfId="121" priority="145" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="148" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="120" priority="144" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K27 AD5:AE27">
-    <cfRule type="cellIs" dxfId="119" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="95" operator="equal">
+      <formula>"p11"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="93" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="94" operator="equal">
       <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="95" operator="equal">
-      <formula>"p11"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="116" priority="96" operator="equal">
       <formula>"p10"</formula>
@@ -57024,69 +57023,69 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K27 AE5:AE27">
-    <cfRule type="cellIs" dxfId="114" priority="98" operator="equal">
-      <formula>"p8"</formula>
+    <cfRule type="cellIs" dxfId="114" priority="105" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="99" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="102" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="104" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="103" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="101" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="100" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="99" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="100" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="101" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="102" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="103" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="104" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="105" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="107" priority="98" operator="equal">
+      <formula>"p8"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:O4">
-    <cfRule type="cellIs" dxfId="106" priority="135" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="138" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="141" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="140" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="139" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="136" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="101" priority="135" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="136" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="137" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="137" operator="equal">
       <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="138" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="139" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="140" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="141" operator="equal">
-      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O27">
-    <cfRule type="cellIs" dxfId="99" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="84" operator="equal">
+      <formula>"p9"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="82" operator="equal">
+      <formula>"p11"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="81" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="80" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="81" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="82" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="83" operator="equal">
       <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="84" operator="equal">
-      <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O27">
@@ -57119,106 +57118,106 @@
     <cfRule type="cellIs" dxfId="86" priority="128" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="129" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="85" priority="134" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="133" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="132" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="131" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="130" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="131" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="132" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="133" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="134" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="80" priority="129" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:S27">
-    <cfRule type="cellIs" dxfId="79" priority="67" operator="equal">
-      <formula>"p13"</formula>
+    <cfRule type="cellIs" dxfId="79" priority="71" operator="equal">
+      <formula>"p9"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="78" priority="68" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="70" operator="equal">
+      <formula>"p10"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="69" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="70" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="71" operator="equal">
-      <formula>"p9"</formula>
+    <cfRule type="cellIs" dxfId="75" priority="67" operator="equal">
+      <formula>"p13"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S27">
-    <cfRule type="cellIs" dxfId="74" priority="72" operator="equal">
-      <formula>"p8"</formula>
+    <cfRule type="cellIs" dxfId="74" priority="76" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="73" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="73" priority="75" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="72" priority="74" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="75" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="71" priority="73" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="76" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="70" priority="72" operator="equal">
+      <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="77" operator="equal">
-      <formula>"p3"</formula>
+    <cfRule type="cellIs" dxfId="69" priority="79" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="68" priority="78" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="79" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="67" priority="77" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V4:W4">
-    <cfRule type="cellIs" dxfId="66" priority="121" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="122" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="122" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="123" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="127" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="126" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="125" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="124" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="123" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="124" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="125" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="126" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="127" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="60" priority="121" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W27">
     <cfRule type="cellIs" dxfId="59" priority="54" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="55" operator="equal">
-      <formula>"p12"</formula>
+    <cfRule type="cellIs" dxfId="58" priority="57" operator="equal">
+      <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="58" operator="equal">
+      <formula>"p9"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="56" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="57" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="58" operator="equal">
-      <formula>"p9"</formula>
+    <cfRule type="cellIs" dxfId="55" priority="55" operator="equal">
+      <formula>"p12"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W27">
@@ -57240,22 +57239,22 @@
     <cfRule type="cellIs" dxfId="49" priority="64" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="66" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="65" operator="equal">
       <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="66" operator="equal">
-      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:AA4">
-    <cfRule type="cellIs" dxfId="46" priority="114" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="46" priority="116" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="45" priority="115" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="116" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="44" priority="114" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="43" priority="117" operator="equal">
       <formula>"p4"</formula>
@@ -57280,126 +57279,126 @@
     <cfRule type="cellIs" dxfId="37" priority="43" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="45" operator="equal">
+      <formula>"p9"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="44" operator="equal">
       <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="45" operator="equal">
-      <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA5:AA27">
-    <cfRule type="cellIs" dxfId="34" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="48" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="53" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="52" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="51" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="49" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="47" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="47" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="48" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="49" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="50" operator="equal">
       <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="51" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="52" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="53" operator="equal">
-      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD4:AE4">
-    <cfRule type="cellIs" dxfId="26" priority="34" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="26" priority="38" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="35" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="25" priority="37" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="24" priority="36" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="37" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="23" priority="35" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="38" operator="equal">
-      <formula>"p3"</formula>
+    <cfRule type="cellIs" dxfId="22" priority="34" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="40" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="39" operator="equal">
       <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="40" operator="equal">
-      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH4:AI4">
-    <cfRule type="cellIs" dxfId="19" priority="14" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
+      <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="18" priority="17" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="19" operator="equal">
-      <formula>"p2"</formula>
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
       <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH5:AI27">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>"p9"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"p13"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI5:AI27">
     <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="11" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -57411,23 +57410,23 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E45570FC-AD57-4C4E-AD9C-A3B1E85C5742}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" customWidth="1"/>
-    <col min="11" max="11" width="44.08984375" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.21875" customWidth="1"/>
+    <col min="11" max="11" width="44.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -57450,7 +57449,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -57473,7 +57472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -57502,7 +57501,7 @@
         <v>9.9342776262546797E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -57531,7 +57530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -57560,7 +57559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -57589,7 +57588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -57618,7 +57617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -57647,7 +57646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -57676,7 +57675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -57705,7 +57704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -57734,7 +57733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -57763,7 +57762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -57792,8 +57791,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>68</v>
       </c>
@@ -57804,7 +57803,7 @@
       <c r="G16" s="36"/>
       <c r="H16" s="37"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -57813,7 +57812,7 @@
       <c r="G17" s="39"/>
       <c r="H17" s="40"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -57822,7 +57821,7 @@
       <c r="G18" s="39"/>
       <c r="H18" s="40"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -57831,7 +57830,7 @@
       <c r="G19" s="39"/>
       <c r="H19" s="40"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -57840,7 +57839,7 @@
       <c r="G20" s="39"/>
       <c r="H20" s="40"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -57849,7 +57848,7 @@
       <c r="G21" s="39"/>
       <c r="H21" s="40"/>
     </row>
-    <row r="22" spans="2:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -57858,7 +57857,7 @@
       <c r="G22" s="39"/>
       <c r="H22" s="40"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -57867,7 +57866,7 @@
       <c r="G23" s="39"/>
       <c r="H23" s="40"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -57876,7 +57875,7 @@
       <c r="G24" s="39"/>
       <c r="H24" s="40"/>
     </row>
-    <row r="25" spans="2:8" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" ht="88.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -57898,25 +57897,25 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE4FFD-F878-482C-A0A8-BDAA2E8CFFC3}">
   <dimension ref="A1:J25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" customWidth="1"/>
-    <col min="13" max="13" width="48.81640625" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.21875" customWidth="1"/>
+    <col min="13" max="13" width="48.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -57945,7 +57944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -57974,7 +57973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -58011,7 +58010,7 @@
         <v>8.2508191738560901E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -58048,7 +58047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -58085,7 +58084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -58122,7 +58121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -58159,7 +58158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -58196,7 +58195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -58233,7 +58232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -58270,7 +58269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -58307,7 +58306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -58344,7 +58343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -58381,8 +58380,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:10" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>70</v>
       </c>
@@ -58395,7 +58394,7 @@
       <c r="I16" s="36"/>
       <c r="J16" s="37"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -58406,7 +58405,7 @@
       <c r="I17" s="39"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -58417,7 +58416,7 @@
       <c r="I18" s="39"/>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -58428,7 +58427,7 @@
       <c r="I19" s="39"/>
       <c r="J19" s="40"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -58439,7 +58438,7 @@
       <c r="I20" s="39"/>
       <c r="J20" s="40"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -58450,7 +58449,7 @@
       <c r="I21" s="39"/>
       <c r="J21" s="40"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -58461,7 +58460,7 @@
       <c r="I22" s="39"/>
       <c r="J22" s="40"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -58472,7 +58471,7 @@
       <c r="I23" s="39"/>
       <c r="J23" s="40"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -58483,7 +58482,7 @@
       <c r="I24" s="39"/>
       <c r="J24" s="40"/>
     </row>
-    <row r="25" spans="2:10" ht="141" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" ht="141" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -58507,21 +58506,21 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB08D38-758B-4C93-953E-47B034B6B7A0}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -58544,7 +58543,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -58567,7 +58566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -58596,7 +58595,7 @@
         <v>9.5258521600517301E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -58625,7 +58624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -58654,7 +58653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -58683,7 +58682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -58712,7 +58711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -58741,7 +58740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -58770,7 +58769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -58799,7 +58798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -58828,7 +58827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -58857,7 +58856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -58886,8 +58885,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>71</v>
       </c>
@@ -58898,7 +58897,7 @@
       <c r="G16" s="36"/>
       <c r="H16" s="37"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -58907,7 +58906,7 @@
       <c r="G17" s="39"/>
       <c r="H17" s="40"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -58916,7 +58915,7 @@
       <c r="G18" s="39"/>
       <c r="H18" s="40"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -58925,7 +58924,7 @@
       <c r="G19" s="39"/>
       <c r="H19" s="40"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -58934,7 +58933,7 @@
       <c r="G20" s="39"/>
       <c r="H20" s="40"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -58943,7 +58942,7 @@
       <c r="G21" s="39"/>
       <c r="H21" s="40"/>
     </row>
-    <row r="22" spans="2:8" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="87" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -58952,7 +58951,7 @@
       <c r="G22" s="39"/>
       <c r="H22" s="40"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -58961,7 +58960,7 @@
       <c r="G23" s="39"/>
       <c r="H23" s="40"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -58970,7 +58969,7 @@
       <c r="G24" s="39"/>
       <c r="H24" s="40"/>
     </row>
-    <row r="25" spans="2:8" ht="74.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" ht="74.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -58992,24 +58991,24 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07F82A79-2B4A-4137-852C-755DEDCA5B93}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -59041,7 +59040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -59073,7 +59072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -59114,7 +59113,7 @@
         <v>4.3002817262355102E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -59155,7 +59154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -59196,7 +59195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -59237,7 +59236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -59278,7 +59277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -59319,7 +59318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -59360,7 +59359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -59401,7 +59400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -59442,7 +59441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -59483,7 +59482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -59524,8 +59523,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>76</v>
       </c>
@@ -59539,7 +59538,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -59551,7 +59550,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -59563,7 +59562,7 @@
       <c r="J18" s="39"/>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -59575,7 +59574,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -59587,7 +59586,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -59599,7 +59598,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -59611,7 +59610,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -59623,7 +59622,7 @@
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -59635,7 +59634,7 @@
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
     </row>
-    <row r="25" spans="2:11" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -59660,23 +59659,23 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C74488B-26AE-49B8-83E1-BFE79ADC2E4A}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -59708,7 +59707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -59740,7 +59739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -59781,7 +59780,7 @@
         <v>4.6752827482718001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -59822,7 +59821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -59863,7 +59862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -59904,7 +59903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -59945,7 +59944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -59986,7 +59985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -60027,7 +60026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -60068,7 +60067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -60109,7 +60108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -60150,7 +60149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -60191,8 +60190,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>72</v>
       </c>
@@ -60206,7 +60205,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -60218,7 +60217,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -60230,7 +60229,7 @@
       <c r="J18" s="39"/>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -60242,7 +60241,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -60254,7 +60253,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -60266,7 +60265,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" ht="69.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" ht="69.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -60278,7 +60277,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -60290,7 +60289,7 @@
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -60302,7 +60301,7 @@
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
     </row>
-    <row r="25" spans="2:11" ht="62.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" ht="62.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -60327,22 +60326,22 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617D1657-68E6-425A-BEC6-156568C1CA34}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -60368,7 +60367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -60394,7 +60393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -60427,7 +60426,7 @@
         <v>0.14268134770565799</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -60460,7 +60459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -60493,7 +60492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -60526,7 +60525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -60559,7 +60558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -60592,7 +60591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -60625,7 +60624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -60658,7 +60657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -60691,7 +60690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -60724,7 +60723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -60757,8 +60756,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>73</v>
       </c>
@@ -60770,7 +60769,7 @@
       <c r="H16" s="36"/>
       <c r="I16" s="37"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -60780,7 +60779,7 @@
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -60790,7 +60789,7 @@
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -60800,7 +60799,7 @@
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -60810,7 +60809,7 @@
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -60820,7 +60819,7 @@
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -60830,7 +60829,7 @@
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -60840,7 +60839,7 @@
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -60850,7 +60849,7 @@
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
     </row>
-    <row r="25" spans="2:9" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:9" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -60873,21 +60872,21 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD025208-EBF5-4B5B-AA05-51C599203D1C}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -60913,7 +60912,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -60939,7 +60938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -60972,7 +60971,7 @@
         <v>5.3630897672221602E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -61005,7 +61004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -61038,7 +61037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -61071,7 +61070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -61104,7 +61103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -61137,7 +61136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -61170,7 +61169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -61203,7 +61202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -61236,7 +61235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -61269,7 +61268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -61302,8 +61301,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>74</v>
       </c>
@@ -61315,7 +61314,7 @@
       <c r="H16" s="36"/>
       <c r="I16" s="37"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -61325,7 +61324,7 @@
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -61335,7 +61334,7 @@
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -61345,7 +61344,7 @@
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -61355,7 +61354,7 @@
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -61365,7 +61364,7 @@
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -61375,7 +61374,7 @@
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -61385,7 +61384,7 @@
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -61395,7 +61394,7 @@
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
     </row>
-    <row r="25" spans="2:9" ht="112.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:9" ht="112.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -61418,23 +61417,23 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9D3998-67DE-4085-A6E8-30E813E46135}">
   <dimension ref="A1:J25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -61463,7 +61462,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -61492,7 +61491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -61529,7 +61528,7 @@
         <v>4.45169383008562E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -61566,7 +61565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -61603,7 +61602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -61640,7 +61639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -61677,7 +61676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -61714,7 +61713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -61751,7 +61750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -61788,7 +61787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -61825,7 +61824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -61862,7 +61861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -61899,8 +61898,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:10" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>79</v>
       </c>
@@ -61913,7 +61912,7 @@
       <c r="I16" s="36"/>
       <c r="J16" s="37"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -61924,7 +61923,7 @@
       <c r="I17" s="39"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -61935,7 +61934,7 @@
       <c r="I18" s="39"/>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -61946,7 +61945,7 @@
       <c r="I19" s="39"/>
       <c r="J19" s="40"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -61957,7 +61956,7 @@
       <c r="I20" s="39"/>
       <c r="J20" s="40"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -61968,7 +61967,7 @@
       <c r="I21" s="39"/>
       <c r="J21" s="40"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -61979,7 +61978,7 @@
       <c r="I22" s="39"/>
       <c r="J22" s="40"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -61990,7 +61989,7 @@
       <c r="I23" s="39"/>
       <c r="J23" s="40"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -62001,7 +62000,7 @@
       <c r="I24" s="39"/>
       <c r="J24" s="40"/>
     </row>
-    <row r="25" spans="2:10" ht="163.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" ht="163.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -62025,25 +62024,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89480051-BCA3-405F-B673-471E1D4EE818}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.26953125" customWidth="1"/>
-    <col min="17" max="17" width="46.54296875" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.21875" customWidth="1"/>
+    <col min="17" max="17" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -62084,7 +62083,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -62125,7 +62124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>28</v>
       </c>
@@ -62178,7 +62177,7 @@
         <v>3.9654043583940202E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -62231,7 +62230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -62284,7 +62283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -62337,7 +62336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -62390,7 +62389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -62443,7 +62442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -62496,7 +62495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -62549,7 +62548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -62602,7 +62601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -62655,7 +62654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -62708,8 +62707,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="6.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="6.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:14" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>64</v>
       </c>
@@ -62726,7 +62725,7 @@
       <c r="M16" s="36"/>
       <c r="N16" s="37"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -62741,7 +62740,7 @@
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -62756,7 +62755,7 @@
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -62771,7 +62770,7 @@
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -62786,7 +62785,7 @@
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -62801,7 +62800,7 @@
       <c r="M21" s="39"/>
       <c r="N21" s="40"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -62816,7 +62815,7 @@
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -62831,7 +62830,7 @@
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -62846,7 +62845,7 @@
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
     </row>
-    <row r="25" spans="2:14" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:14" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -62874,23 +62873,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB6AE84-88BE-4054-A4FA-FD43BA13B48C}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" customWidth="1"/>
     <col min="14" max="14" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -62922,7 +62921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -62954,7 +62953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>28</v>
       </c>
@@ -62995,7 +62994,7 @@
         <v>3.0860294727687199E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -63036,7 +63035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -63077,7 +63076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -63118,7 +63117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -63159,7 +63158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -63200,7 +63199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -63241,7 +63240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -63282,7 +63281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -63323,7 +63322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -63364,7 +63363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -63405,8 +63404,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>65</v>
       </c>
@@ -63420,7 +63419,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -63432,7 +63431,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -63444,7 +63443,7 @@
       <c r="J18" s="39"/>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -63456,7 +63455,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -63468,7 +63467,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -63480,7 +63479,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -63492,7 +63491,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -63504,7 +63503,7 @@
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -63516,7 +63515,7 @@
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
     </row>
-    <row r="25" spans="2:11" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -63541,26 +63540,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A45733F-34D0-4D88-A6B5-E28376F26D12}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" customWidth="1"/>
     <col min="14" max="14" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -63592,7 +63591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -63624,7 +63623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>28</v>
       </c>
@@ -63665,7 +63664,7 @@
         <v>4.6879642406291701E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -63706,7 +63705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -63747,7 +63746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -63788,7 +63787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -63829,7 +63828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -63870,7 +63869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -63911,7 +63910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -63952,7 +63951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -63993,7 +63992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -64034,7 +64033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -64075,8 +64074,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>66</v>
       </c>
@@ -64090,7 +64089,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -64102,7 +64101,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -64114,7 +64113,7 @@
       <c r="J18" s="39"/>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -64126,7 +64125,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -64138,7 +64137,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -64150,7 +64149,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -64162,7 +64161,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -64174,7 +64173,7 @@
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -64186,7 +64185,7 @@
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
     </row>
-    <row r="25" spans="2:11" ht="98.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" ht="98.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -64211,25 +64210,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B720F0-81EA-4B55-8BF5-5CBED46DDED6}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" customWidth="1"/>
-    <col min="14" max="14" width="46.6328125" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" customWidth="1"/>
+    <col min="14" max="14" width="46.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -64261,7 +64260,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -64293,7 +64292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -64334,7 +64333,7 @@
         <v>4.3716405074177601E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -64375,7 +64374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -64416,7 +64415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -64457,7 +64456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -64498,7 +64497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -64539,7 +64538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -64580,7 +64579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -64621,7 +64620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -64662,7 +64661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -64703,7 +64702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -64744,8 +64743,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>67</v>
       </c>
@@ -64759,7 +64758,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -64771,7 +64770,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -64783,7 +64782,7 @@
       <c r="J18" s="39"/>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -64795,7 +64794,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -64807,7 +64806,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -64819,7 +64818,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -64831,7 +64830,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -64843,7 +64842,7 @@
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -64855,7 +64854,7 @@
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
     </row>
-    <row r="25" spans="2:11" ht="146" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" ht="145.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -64880,25 +64879,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCF9B40-470A-4DE1-8AB1-26EEC2BE06FE}">
   <dimension ref="A1:J25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" customWidth="1"/>
-    <col min="13" max="13" width="47.6328125" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.21875" customWidth="1"/>
+    <col min="13" max="13" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -64927,7 +64926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -64956,7 +64955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>28</v>
       </c>
@@ -64993,7 +64992,7 @@
         <v>3.9819587215948797E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -65030,7 +65029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -65067,7 +65066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -65104,7 +65103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -65141,7 +65140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -65178,7 +65177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -65215,7 +65214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -65252,7 +65251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -65289,7 +65288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -65326,7 +65325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -65363,8 +65362,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:10" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>69</v>
       </c>
@@ -65377,7 +65376,7 @@
       <c r="I16" s="36"/>
       <c r="J16" s="37"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -65388,7 +65387,7 @@
       <c r="I17" s="39"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -65399,7 +65398,7 @@
       <c r="I18" s="39"/>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -65410,7 +65409,7 @@
       <c r="I19" s="39"/>
       <c r="J19" s="40"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -65421,7 +65420,7 @@
       <c r="I20" s="39"/>
       <c r="J20" s="40"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -65432,7 +65431,7 @@
       <c r="I21" s="39"/>
       <c r="J21" s="40"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -65443,7 +65442,7 @@
       <c r="I22" s="39"/>
       <c r="J22" s="40"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -65454,7 +65453,7 @@
       <c r="I23" s="39"/>
       <c r="J23" s="40"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -65465,7 +65464,7 @@
       <c r="I24" s="39"/>
       <c r="J24" s="40"/>
     </row>
-    <row r="25" spans="2:10" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" ht="116.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -65489,26 +65488,26 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2F1193-B282-4C78-B1F9-98CD94BECEC3}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.90625" customWidth="1"/>
-    <col min="11" max="11" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" customWidth="1"/>
-    <col min="14" max="14" width="47.6328125" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" customWidth="1"/>
+    <col min="11" max="11" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" customWidth="1"/>
+    <col min="14" max="14" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -65540,7 +65539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -65572,7 +65571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>28</v>
       </c>
@@ -65613,7 +65612,7 @@
         <v>4.0093506851275197E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -65654,7 +65653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -65695,7 +65694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -65736,7 +65735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -65777,7 +65776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -65818,7 +65817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -65859,7 +65858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -65900,7 +65899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -65941,7 +65940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -65982,7 +65981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -66023,8 +66022,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>80</v>
       </c>
@@ -66038,7 +66037,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -66050,7 +66049,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -66062,7 +66061,7 @@
       <c r="J18" s="39"/>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -66074,7 +66073,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -66086,7 +66085,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -66098,7 +66097,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -66110,7 +66109,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -66122,7 +66121,7 @@
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -66134,7 +66133,7 @@
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
     </row>
-    <row r="25" spans="2:11" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" ht="116.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -66159,24 +66158,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80A2506-0B9F-4B14-ADA0-702CD03037C2}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.08984375" customWidth="1"/>
-    <col min="11" max="11" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" customWidth="1"/>
-    <col min="14" max="14" width="46.08984375" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="11" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" customWidth="1"/>
+    <col min="14" max="14" width="46.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -66208,7 +66207,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -66240,7 +66239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -66281,7 +66280,7 @@
         <v>9.8662574579824594E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -66322,7 +66321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -66363,7 +66362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -66404,7 +66403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -66445,7 +66444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -66486,7 +66485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -66527,7 +66526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -66568,7 +66567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -66609,7 +66608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -66650,7 +66649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -66691,8 +66690,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>68</v>
       </c>
@@ -66706,7 +66705,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -66718,7 +66717,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -66730,7 +66729,7 @@
       <c r="J18" s="39"/>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -66742,7 +66741,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -66754,7 +66753,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -66766,7 +66765,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -66778,7 +66777,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -66790,7 +66789,7 @@
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -66802,7 +66801,7 @@
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
     </row>
-    <row r="25" spans="2:11" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" ht="116.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
@@ -66827,25 +66826,25 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FB0C85-64F4-4D82-8FA2-89FE65C5C7BA}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.08984375" customWidth="1"/>
-    <col min="11" max="11" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" customWidth="1"/>
-    <col min="14" max="14" width="45.81640625" customWidth="1"/>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="11" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" customWidth="1"/>
+    <col min="14" max="14" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -66877,7 +66876,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -66909,7 +66908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
@@ -66950,7 +66949,7 @@
         <v>0.11048659654134101</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -66991,7 +66990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -67032,7 +67031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -67073,7 +67072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -67114,7 +67113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -67155,7 +67154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -67196,7 +67195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -67237,7 +67236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -67278,7 +67277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -67319,7 +67318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
@@ -67360,8 +67359,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
         <v>75</v>
       </c>
@@ -67375,7 +67374,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -67387,7 +67386,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -67399,7 +67398,7 @@
       <c r="J18" s="39"/>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
@@ -67411,7 +67410,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -67423,7 +67422,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -67435,7 +67434,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" ht="74" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" ht="73.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -67447,7 +67446,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -67459,7 +67458,7 @@
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -67471,7 +67470,7 @@
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
     </row>
-    <row r="25" spans="2:11" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
